--- a/crd_test_cases.xlsx
+++ b/crd_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="59">
   <si>
     <t>Test ID</t>
   </si>
@@ -82,10 +82,13 @@
     <t>Current % already equals target % across portfolio</t>
   </si>
   <si>
-    <t>X</t>
+    <t>A</t>
   </si>
   <si>
-    <t>Z</t>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
   <si>
     <t>Test-3</t>
@@ -98,15 +101,6 @@
   </si>
   <si>
     <t>Large total asset value across a mixed over/under/on-target portfolio</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
   <si>
     <t>D</t>
@@ -820,7 +814,7 @@
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
       <c r="D8" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E8" s="4">
         <v>30.0</v>
@@ -859,7 +853,7 @@
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
       <c r="D9" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="4">
         <v>50.0</v>
@@ -895,10 +889,10 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="6">
         <v>200000.0</v>
@@ -942,16 +936,16 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="9">
         <v>1.0E9</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E11" s="10">
         <v>30.0</v>
@@ -990,7 +984,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="13"/>
       <c r="D12" s="8" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E12" s="10">
         <v>10.0</v>
@@ -1029,7 +1023,7 @@
       <c r="B13" s="12"/>
       <c r="C13" s="13"/>
       <c r="D13" s="8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E13" s="10">
         <v>15.0</v>
@@ -1068,7 +1062,7 @@
       <c r="B14" s="12"/>
       <c r="C14" s="13"/>
       <c r="D14" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E14" s="10">
         <v>25.0</v>
@@ -1107,7 +1101,7 @@
       <c r="B15" s="12"/>
       <c r="C15" s="13"/>
       <c r="D15" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" s="10">
         <v>20.0</v>
@@ -1143,16 +1137,16 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C16" s="6">
         <v>100000.0</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E16" s="4">
         <v>20.0</v>
@@ -1164,10 +1158,10 @@
         <v>0.0</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>14</v>
@@ -1190,16 +1184,16 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="6">
         <v>100000.0</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E17" s="4">
         <v>20.0</v>
@@ -1211,10 +1205,10 @@
         <v>-10.0</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>14</v>
@@ -1237,16 +1231,16 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="6">
         <v>100000.0</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E18" s="4">
         <v>0.0</v>
@@ -1284,16 +1278,16 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" s="6">
         <v>100000.0</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E19" s="4">
         <v>20.0</v>
@@ -1331,16 +1325,16 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C20" s="4">
         <v>0.0</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E20" s="4">
         <v>20.0</v>
@@ -1378,16 +1372,16 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C21" s="6">
         <v>100000.0</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E21" s="4">
         <v>20.0001</v>
@@ -1425,16 +1419,16 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C22" s="6">
         <v>100000.0</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E22" s="4">
         <v>20.0</v>
@@ -1446,10 +1440,10 @@
         <v>150.0</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>14</v>
@@ -1475,7 +1469,7 @@
       <c r="B23" s="5"/>
       <c r="C23" s="6"/>
       <c r="D23" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E23" s="4">
         <v>20.0</v>
@@ -1487,10 +1481,10 @@
         <v>90.0</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>14</v>
@@ -1516,7 +1510,7 @@
       <c r="B24" s="5"/>
       <c r="C24" s="6"/>
       <c r="D24" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E24" s="4">
         <v>20.0</v>
@@ -1528,10 +1522,10 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>14</v>
@@ -1554,16 +1548,16 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25" s="6">
         <v>-100000.0</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E25" s="4">
         <v>20.0</v>
@@ -1575,10 +1569,10 @@
         <v>100.0</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>14</v>
@@ -1601,16 +1595,16 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C26" s="6">
         <v>100000.0</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E26" s="4">
         <v>-5.0</v>
@@ -1622,10 +1616,10 @@
         <v>100.0</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>14</v>
@@ -1661,10 +1655,10 @@
         <v>100.0</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>14</v>
@@ -1687,16 +1681,16 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C28" s="6">
         <v>100000.0</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E28" s="4">
         <v>20.0</v>
@@ -1708,10 +1702,10 @@
         <v>100.0</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>14</v>
@@ -1745,10 +1739,10 @@
         <v>100.0</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>14</v>
@@ -1771,31 +1765,31 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C30" s="6">
         <v>100000.0</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="I30" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>14</v>
